--- a/backend/data/uploads/MES/2026-07-14_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-14_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{253F56BF-DC46-4530-ACCC-A2A0EB7A04F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24214AA3-6201-4E46-B527-8BA14B47D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9704CDF6-456E-4A93-976C-D11AB99A2B36}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9621A62F-86DF-4F67-AC11-016A699E83F0}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{264849A7-05A6-4B72-8F80-A8F26F3AA2D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C239C9-6DFF-4FD3-BD6C-102F7AFD8D46}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-14_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-14_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24214AA3-6201-4E46-B527-8BA14B47D8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B6C2F0-8A44-49B1-81A7-2A2F14819923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9621A62F-86DF-4F67-AC11-016A699E83F0}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{68C16DD8-6F17-46E2-822C-AA63F59824DE}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C239C9-6DFF-4FD3-BD6C-102F7AFD8D46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46B740C-AB36-444E-8020-5FBE5D12EC42}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-14_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-14_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B6C2F0-8A44-49B1-81A7-2A2F14819923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2F7D2B0-90D0-4FAE-B3F6-48CE7B580421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{68C16DD8-6F17-46E2-822C-AA63F59824DE}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{037723CC-EE29-4E59-9186-26F403830A53}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B46B740C-AB36-444E-8020-5FBE5D12EC42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DEDD52-4803-4E20-91E6-95EE58FD4F7B}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
